--- a/Configs/GameConfig/Datas/__beans__.xlsx
+++ b/Configs/GameConfig/Datas/__beans__.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="11700"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="64">
   <si>
     <t>##var</t>
   </si>
@@ -101,6 +101,9 @@
     <t>,</t>
   </si>
   <si>
+    <t>道具转化</t>
+  </si>
+  <si>
     <t>id</t>
   </si>
   <si>
@@ -114,6 +117,18 @@
   </si>
   <si>
     <t>道具数量</t>
+  </si>
+  <si>
+    <t>item.RewardData</t>
+  </si>
+  <si>
+    <t>通用道具奖励</t>
+  </si>
+  <si>
+    <t>item.ConsumeItem</t>
+  </si>
+  <si>
+    <t>通用道具消耗</t>
   </si>
   <si>
     <t>test.TestExcelBean1</t>
@@ -369,7 +384,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -390,6 +405,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.05"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -487,12 +514,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -695,7 +716,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -719,16 +740,16 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -743,97 +764,109 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="23" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="22" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1154,14 +1187,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P16"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
+  <dimension ref="A1:P26"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="2" max="4" width="20.625" customWidth="1"/>
     <col min="5" max="6" width="12.25" customWidth="1"/>
     <col min="7" max="9" width="15" customWidth="1"/>
-    <col min="10" max="12" width="13.5089285714286" customWidth="1"/>
-    <col min="13" max="13" width="10.3839285714286" customWidth="1"/>
+    <col min="10" max="12" width="13.5083333333333" customWidth="1"/>
+    <col min="13" max="13" width="10.3833333333333" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1192,15 +1225,15 @@
       <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="4"/>
-      <c r="L1" s="4"/>
-      <c r="M1" s="4"/>
-      <c r="N1" s="4"/>
-      <c r="O1" s="4"/>
-      <c r="P1" s="4"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+      <c r="O1" s="2"/>
+      <c r="P1" s="2"/>
     </row>
     <row r="2" spans="1:16">
       <c r="A2" s="1" t="s">
@@ -1257,220 +1290,351 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="2:14">
-      <c r="B4" s="2" t="s">
+    <row r="4" spans="1:16">
+      <c r="B4" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="F4" s="2"/>
-      <c r="J4" s="2" t="s">
+      <c r="F4" s="3"/>
+      <c r="G4" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2" t="s">
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="N4" s="2" t="s">
+      <c r="K4" s="3"/>
+      <c r="L4" s="3" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="5" spans="10:14">
-      <c r="J5" s="2" t="s">
+      <c r="M4" s="4"/>
+      <c r="N4" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="K5" s="2"/>
-      <c r="L5" s="2" t="s">
+      <c r="O4" s="4"/>
+      <c r="P4" s="4"/>
+    </row>
+    <row r="5" spans="1:16">
+      <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="K5" s="3"/>
+      <c r="L5" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="M5" s="4"/>
+      <c r="N5" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="O5" s="4"/>
+      <c r="P5" s="4"/>
+    </row>
+    <row r="6" spans="1:16">
+      <c r="B6" s="5"/>
+    </row>
+    <row r="7" spans="1:16">
+      <c r="B7" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" s="7"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="H7" s="7"/>
+      <c r="I7" s="7"/>
+      <c r="J7" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="N5" s="2" t="s">
+      <c r="K7" s="6"/>
+      <c r="L7" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M7" s="7"/>
+      <c r="N7" s="6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16">
+      <c r="B8" s="6"/>
+      <c r="C8" s="7"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="7"/>
+      <c r="H8" s="7"/>
+      <c r="I8" s="7"/>
+      <c r="J8" s="6" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="6" spans="2:14">
-      <c r="B6" s="2" t="s">
+      <c r="K8" s="6"/>
+      <c r="L8" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M8" s="7"/>
+      <c r="N8" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="G6" t="s">
-        <v>30</v>
-      </c>
-      <c r="J6" t="s">
-        <v>31</v>
-      </c>
-      <c r="L6" t="s">
+    </row>
+    <row r="9" spans="1:16">
+      <c r="B9" s="5"/>
+    </row>
+    <row r="10" spans="1:16">
+      <c r="B10" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" s="7"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="7"/>
+      <c r="G10" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="H10" s="7"/>
+      <c r="I10" s="7"/>
+      <c r="J10" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="N6" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="7" spans="10:14">
-      <c r="J7" t="s">
-        <v>33</v>
-      </c>
-      <c r="L7" t="s">
+      <c r="K10" s="6"/>
+      <c r="L10" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M10" s="7"/>
+      <c r="N10" s="6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16">
+      <c r="B11" s="6"/>
+      <c r="C11" s="7"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="7"/>
+      <c r="G11" s="7"/>
+      <c r="H11" s="7"/>
+      <c r="I11" s="7"/>
+      <c r="J11" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="K11" s="6"/>
+      <c r="L11" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M11" s="7"/>
+      <c r="N11" s="6" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16">
+      <c r="B12" s="5"/>
+    </row>
+    <row r="13" spans="1:16">
+      <c r="B13" s="5"/>
+    </row>
+    <row r="14" spans="1:16">
+      <c r="B14" s="5"/>
+    </row>
+    <row r="15" spans="1:16">
+      <c r="B15" s="5"/>
+    </row>
+    <row r="16" spans="1:16">
+      <c r="B16" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="N7" t="s">
+      <c r="G16" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="8" spans="10:14">
-      <c r="J8" t="s">
+      <c r="J16" t="s">
         <v>36</v>
       </c>
-      <c r="L8" t="s">
-        <v>25</v>
-      </c>
-      <c r="N8" t="s">
+      <c r="L16" t="s">
+        <v>26</v>
+      </c>
+      <c r="N16" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="9" spans="10:14">
-      <c r="J9" t="s">
+    <row r="17" spans="2:14">
+      <c r="J17" t="s">
         <v>38</v>
       </c>
-      <c r="L9" t="s">
+      <c r="L17" t="s">
         <v>39</v>
       </c>
-      <c r="N9" t="s">
+      <c r="N17" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="10" spans="2:14">
-      <c r="B10" t="s">
+    <row r="18" spans="2:14">
+      <c r="J18" t="s">
         <v>41</v>
       </c>
-      <c r="G10" t="s">
-        <v>30</v>
-      </c>
-      <c r="J10" t="s">
+      <c r="L18" t="s">
+        <v>26</v>
+      </c>
+      <c r="N18" t="s">
         <v>42</v>
       </c>
-      <c r="L10" t="s">
-        <v>25</v>
-      </c>
-      <c r="N10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="11" spans="10:14">
-      <c r="J11" t="s">
+    </row>
+    <row r="19" spans="2:14">
+      <c r="J19" t="s">
         <v>43</v>
       </c>
-      <c r="L11" t="s">
-        <v>34</v>
-      </c>
-      <c r="N11" t="s">
+      <c r="L19" t="s">
+        <v>44</v>
+      </c>
+      <c r="N19" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="20" spans="2:14">
+      <c r="B20" t="s">
+        <v>46</v>
+      </c>
+      <c r="G20" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="12" spans="10:14">
-      <c r="J12" t="s">
+      <c r="J20" t="s">
+        <v>47</v>
+      </c>
+      <c r="L20" t="s">
+        <v>26</v>
+      </c>
+      <c r="N20" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="21" spans="2:14">
+      <c r="J21" t="s">
+        <v>48</v>
+      </c>
+      <c r="L21" t="s">
+        <v>39</v>
+      </c>
+      <c r="N21" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="22" spans="2:14">
+      <c r="J22" t="s">
+        <v>49</v>
+      </c>
+      <c r="L22" t="s">
         <v>44</v>
       </c>
-      <c r="L12" t="s">
-        <v>39</v>
-      </c>
-      <c r="N12" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="13" spans="2:14">
-      <c r="B13" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
-      <c r="J13" s="3"/>
-      <c r="K13" s="3"/>
-      <c r="L13" s="3"/>
-      <c r="M13" s="3"/>
-      <c r="N13" s="3"/>
-    </row>
-    <row r="14" spans="2:14">
-      <c r="B14" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
-      <c r="J14" s="3" t="s">
+      <c r="N22" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="23" spans="2:14">
+      <c r="B23" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="K14" s="3"/>
-      <c r="L14" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M14" s="3"/>
-      <c r="N14" s="3" t="s">
+      <c r="C23" s="8"/>
+      <c r="D23" s="8"/>
+      <c r="E23" s="8"/>
+      <c r="F23" s="8"/>
+      <c r="G23" s="8"/>
+      <c r="H23" s="8"/>
+      <c r="I23" s="8"/>
+      <c r="J23" s="8"/>
+      <c r="K23" s="8"/>
+      <c r="L23" s="8"/>
+      <c r="M23" s="8"/>
+      <c r="N23" s="8"/>
+    </row>
+    <row r="24" spans="2:14">
+      <c r="B24" s="8" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="15" spans="2:14">
-      <c r="B15" s="3" t="s">
+      <c r="C24" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="C15" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3" t="s">
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="G15" s="3" t="s">
+      <c r="G24" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
-      <c r="J15" s="3" t="s">
+      <c r="H24" s="8"/>
+      <c r="I24" s="8"/>
+      <c r="J24" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="K15" s="3"/>
-      <c r="L15" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M15" s="3"/>
-      <c r="N15" s="3" t="s">
+      <c r="K24" s="8"/>
+      <c r="L24" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="M24" s="8"/>
+      <c r="N24" s="8" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="16" spans="2:14">
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3"/>
-      <c r="J16" s="3" t="s">
+    <row r="25" spans="2:14">
+      <c r="B25" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="K16" s="3"/>
-      <c r="L16" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M16" s="3"/>
-      <c r="N16" s="3" t="s">
+      <c r="C25" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="D25" s="8"/>
+      <c r="E25" s="8"/>
+      <c r="F25" s="8" t="s">
         <v>58</v>
+      </c>
+      <c r="G25" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="H25" s="8"/>
+      <c r="I25" s="8"/>
+      <c r="J25" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="K25" s="8"/>
+      <c r="L25" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="M25" s="8"/>
+      <c r="N25" s="8" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="26" spans="2:14">
+      <c r="B26" s="8"/>
+      <c r="C26" s="8"/>
+      <c r="D26" s="8"/>
+      <c r="E26" s="8"/>
+      <c r="F26" s="8"/>
+      <c r="G26" s="8"/>
+      <c r="H26" s="8"/>
+      <c r="I26" s="8"/>
+      <c r="J26" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="K26" s="8"/>
+      <c r="L26" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="M26" s="8"/>
+      <c r="N26" s="8" t="s">
+        <v>63</v>
       </c>
     </row>
   </sheetData>
